--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0003T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.16666685623681</v>
+        <v>5.389583364138482</v>
       </c>
       <c r="D2" t="n">
-        <v>31.54049714890122</v>
+        <v>5.125330786696447</v>
       </c>
       <c r="E2" t="n">
-        <v>9.831423012400803</v>
+        <v>1.59760623951513</v>
       </c>
       <c r="F2" t="n">
-        <v>9.687831285881623</v>
+        <v>1.574272583955764</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.09074718568989</v>
+        <v>5.214746417674608</v>
       </c>
       <c r="D3" t="n">
-        <v>30.97134919198339</v>
+        <v>5.032844243697301</v>
       </c>
       <c r="E3" t="n">
-        <v>9.831423012400803</v>
+        <v>1.59760623951513</v>
       </c>
       <c r="F3" t="n">
-        <v>9.687831285881623</v>
+        <v>1.574272583955764</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.71257088800262</v>
+        <v>5.803292769300425</v>
       </c>
       <c r="D4" t="n">
-        <v>36.75653896218029</v>
+        <v>5.972937581354298</v>
       </c>
       <c r="E4" t="n">
-        <v>9.831423012400803</v>
+        <v>1.59760623951513</v>
       </c>
       <c r="F4" t="n">
-        <v>9.687831285881623</v>
+        <v>1.574272583955764</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.17215008278705</v>
+        <v>3.277974388452896</v>
       </c>
       <c r="D5" t="n">
-        <v>20.44940623348145</v>
+        <v>3.323028512940736</v>
       </c>
       <c r="E5" t="n">
-        <v>9.831423012400803</v>
+        <v>1.59760623951513</v>
       </c>
       <c r="F5" t="n">
-        <v>9.687831285881623</v>
+        <v>1.574272583955764</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.90131964700964</v>
+        <v>5.833964442639068</v>
       </c>
       <c r="D6" t="n">
-        <v>34.81241771482646</v>
+        <v>5.6570178786593</v>
       </c>
       <c r="E6" t="n">
-        <v>9.831423012400803</v>
+        <v>1.59760623951513</v>
       </c>
       <c r="F6" t="n">
-        <v>9.687831285881623</v>
+        <v>1.574272583955764</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.87607597180158</v>
+        <v>6.804862345417757</v>
       </c>
       <c r="D7" t="n">
-        <v>41.36642716954219</v>
+        <v>6.722044415050607</v>
       </c>
       <c r="E7" t="n">
-        <v>9.831423012400803</v>
+        <v>1.59760623951513</v>
       </c>
       <c r="F7" t="n">
-        <v>9.687831285881623</v>
+        <v>1.574272583955764</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.17532897686577</v>
+        <v>5.715990958740688</v>
       </c>
       <c r="D8" t="n">
-        <v>35.81055419598183</v>
+        <v>5.819215056847048</v>
       </c>
       <c r="E8" t="n">
-        <v>9.831423012400803</v>
+        <v>1.59760623951513</v>
       </c>
       <c r="F8" t="n">
-        <v>9.687831285881623</v>
+        <v>1.574272583955764</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.22626957948412</v>
+        <v>4.911768806666169</v>
       </c>
       <c r="D9" t="n">
-        <v>30.67987439750202</v>
+        <v>4.985479589594078</v>
       </c>
       <c r="E9" t="n">
-        <v>9.831423012400803</v>
+        <v>1.59760623951513</v>
       </c>
       <c r="F9" t="n">
-        <v>9.687831285881623</v>
+        <v>1.574272583955764</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>35.87107736568741</v>
+        <v>5.829050071924205</v>
       </c>
       <c r="D10" t="n">
-        <v>35.7839337067726</v>
+        <v>5.814889227350548</v>
       </c>
       <c r="E10" t="n">
-        <v>9.831423012400803</v>
+        <v>1.59760623951513</v>
       </c>
       <c r="F10" t="n">
-        <v>9.687831285881623</v>
+        <v>1.574272583955764</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>21.20350841120581</v>
+        <v>3.445570116820944</v>
       </c>
       <c r="D11" t="n">
-        <v>22.08922690419429</v>
+        <v>3.589499371931572</v>
       </c>
       <c r="E11" t="n">
-        <v>9.831423012400803</v>
+        <v>1.59760623951513</v>
       </c>
       <c r="F11" t="n">
-        <v>9.687831285881623</v>
+        <v>1.574272583955764</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>5.3829299132885</v>
+        <v>0.8747261109093812</v>
       </c>
       <c r="D12" t="n">
-        <v>5.273230458313149</v>
+        <v>0.8568999494758868</v>
       </c>
       <c r="E12" t="n">
-        <v>9.831423012400803</v>
+        <v>1.59760623951513</v>
       </c>
       <c r="F12" t="n">
-        <v>9.687831285881623</v>
+        <v>1.574272583955764</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
